--- a/Result/profitability/2524.xlsx
+++ b/Result/profitability/2524.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.49</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>0.9925</v>
       </c>
       <c r="N2" t="n">
-        <v>46.27500000000001</v>
+        <v>46.3625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.12</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09875</v>
+        <v>0.4924999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>44.43375</v>
+        <v>45.7325</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.48</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5187499999999998</v>
+        <v>0.3662499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>43.36625</v>
+        <v>44.68</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.14</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3149999999999998</v>
+        <v>0.3462499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>40.8725</v>
+        <v>41.5525</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.31</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3512499999999999</v>
+        <v>0.3587499999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>38.4325</v>
+        <v>38.45874999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.37</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3712499999999999</v>
+        <v>0.4074999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>35.08625</v>
+        <v>35.49375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.65</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4549999999999998</v>
+        <v>0.4437499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>32.2825</v>
+        <v>32.81375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2524</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>652</v>
+      </c>
+      <c r="D75" t="n">
+        <v>308</v>
+      </c>
+      <c r="E75" t="n">
+        <v>344</v>
+      </c>
+      <c r="F75" t="n">
+        <v>52.79</v>
+      </c>
+      <c r="G75" t="n">
+        <v>193</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>29.58%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-67</v>
+      </c>
+      <c r="J75" t="n">
+        <v>126</v>
+      </c>
+      <c r="K75" t="n">
+        <v>100</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>48.445</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.08999999999999997</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2499999999999999</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.08755665430572734</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.439999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1148891235480465</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
